--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology Bacteriology Observationurine</t>
+    <t>Lab Observation: Microbiology Bacteriology Observation[urine]</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1000,7 +1000,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMicrobiologyUrineScreenResult</t>
+    <t>http://va.gov/fhir/ValueSet/MicrobiologyUrineScreenResult</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1901,7 +1901,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.29296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.56640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2338" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -594,6 +594,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status</t>
   </si>
   <si>
+    <t>2073: target not supported</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -639,6 +642,9 @@
   </si>
   <si>
     <t>open</t>
+  </si>
+  <si>
+    <t>2074: target not supported</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -661,6 +667,9 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>2075: target not supported</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -689,6 +698,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>2076: target not supported</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -726,6 +738,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>2077: target not supported</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -815,6 +830,10 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-1
 </t>
   </si>
@@ -835,6 +854,19 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>2078: target not supported</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -907,10 +939,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>obs-7
 us-core-2us-core-3us-core-4</t>
   </si>
@@ -1045,6 +1073,28 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2079: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>2080: target not supported</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1066,6 +1116,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>2081: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1873,7 +1926,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR57"/>
+  <dimension ref="A1:AR60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
@@ -3669,25 +3722,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -3695,10 +3748,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3721,19 +3774,19 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -3761,26 +3814,26 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -3795,7 +3848,7 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -3810,10 +3863,10 @@
         <v>84</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3821,13 +3874,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -3849,19 +3902,19 @@
         <v>84</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>84</v>
@@ -3871,7 +3924,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -3889,10 +3942,10 @@
         <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -3910,7 +3963,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -3925,7 +3978,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -3940,10 +3993,10 @@
         <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3951,14 +4004,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3977,19 +4030,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -4014,13 +4067,13 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -4038,7 +4091,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>94</v>
@@ -4053,36 +4106,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>217</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4105,19 +4158,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4166,7 +4219,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4181,25 +4234,25 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4207,10 +4260,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4233,16 +4286,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4292,7 +4345,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4319,13 +4372,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4333,14 +4386,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4359,19 +4412,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4420,7 +4473,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4441,19 +4494,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4461,14 +4514,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4487,19 +4540,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4536,19 +4589,17 @@
         <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4557,10 +4608,10 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -4569,19 +4620,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4589,14 +4640,16 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4606,7 +4659,7 @@
         <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>84</v>
@@ -4615,18 +4668,20 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
       </c>
@@ -4674,7 +4729,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4683,31 +4738,31 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AQ22" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4715,10 +4770,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4729,7 +4784,7 @@
         <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>84</v>
@@ -4741,18 +4796,18 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>84</v>
       </c>
@@ -4800,13 +4855,13 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>84</v>
@@ -4821,19 +4876,19 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4841,10 +4896,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4855,10 +4910,10 @@
         <v>82</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -4867,17 +4922,15 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N24" t="s" s="2">
         <v>281</v>
       </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>282</v>
       </c>
@@ -4916,65 +4969,65 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AC24" s="2"/>
-      <c r="AD24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AR24" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>84</v>
       </c>
@@ -4995,19 +5048,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5044,19 +5097,17 @@
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5065,10 +5116,10 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>84</v>
@@ -5080,29 +5131,31 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5114,25 +5167,29 @@
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>294</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5180,7 +5237,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5189,10 +5246,10 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>84</v>
@@ -5204,38 +5261,38 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="AP26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>84</v>
@@ -5247,17 +5304,15 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>140</v>
+        <v>303</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>141</v>
+        <v>304</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5294,31 +5349,31 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>302</v>
+        <v>84</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5336,7 +5391,7 @@
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5347,14 +5402,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5364,29 +5419,27 @@
         <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>307</v>
+        <v>140</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>308</v>
+        <v>141</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5410,26 +5463,28 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AC28" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AA28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>313</v>
@@ -5444,13 +5499,13 @@
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>84</v>
@@ -5459,10 +5514,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5473,10 +5528,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5487,10 +5542,10 @@
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -5499,19 +5554,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5536,13 +5591,11 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5560,13 +5613,13 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>84</v>
@@ -5575,10 +5628,10 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>84</v>
@@ -5604,7 +5657,7 @@
         <v>327</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5618,28 +5671,28 @@
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5664,11 +5717,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>332</v>
+        <v>84</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -5686,7 +5741,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5695,7 +5750,7 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>106</v>
@@ -5713,10 +5768,10 @@
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>137</v>
+        <v>334</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5727,45 +5782,47 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="D31" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>338</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5790,13 +5847,13 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5814,22 +5871,22 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -5838,29 +5895,31 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>346</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>84</v>
       </c>
@@ -5869,31 +5928,31 @@
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>348</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>349</v>
+        <v>289</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>351</v>
+        <v>291</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>352</v>
+        <v>292</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5942,22 +6001,22 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>347</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
@@ -5966,27 +6025,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>353</v>
+        <v>296</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>354</v>
+        <v>297</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6000,7 +6059,7 @@
         <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
@@ -6009,18 +6068,20 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
@@ -6044,13 +6105,11 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6068,7 +6127,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6077,13 +6136,13 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>349</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6092,38 +6151,38 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>363</v>
+        <v>137</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>84</v>
@@ -6135,19 +6194,19 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6172,14 +6231,14 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="Y34" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6196,13 +6255,13 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>84</v>
@@ -6220,27 +6279,27 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6251,7 +6310,7 @@
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>84</v>
@@ -6263,18 +6322,20 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6322,13 +6383,13 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
@@ -6346,27 +6407,27 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6389,16 +6450,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>385</v>
+        <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6424,13 +6485,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>378</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6448,7 +6509,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6472,27 +6533,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6503,7 +6564,7 @@
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>84</v>
@@ -6515,19 +6576,19 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>394</v>
+        <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6552,13 +6613,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6576,19 +6637,19 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>399</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6603,10 +6664,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6617,10 +6678,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6643,15 +6704,17 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>294</v>
+        <v>393</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6700,7 +6763,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>297</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6712,7 +6775,7 @@
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6724,38 +6787,38 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>298</v>
+        <v>399</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
@@ -6767,16 +6830,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>402</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>141</v>
+        <v>403</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>301</v>
+        <v>404</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>143</v>
+        <v>405</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6826,19 +6889,19 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>304</v>
+        <v>401</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -6850,31 +6913,31 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>298</v>
+        <v>408</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6887,25 +6950,25 @@
         <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>140</v>
+        <v>411</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>143</v>
+        <v>414</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>149</v>
+        <v>415</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6954,7 +7017,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6966,7 +7029,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>416</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -6981,10 +7044,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>137</v>
+        <v>418</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6995,10 +7058,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7021,13 +7084,13 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
+        <v>305</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7078,7 +7141,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7087,10 +7150,10 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>413</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>84</v>
@@ -7105,10 +7168,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>415</v>
+        <v>307</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7119,21 +7182,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7145,15 +7208,17 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>410</v>
+        <v>140</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7202,19 +7267,19 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>313</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>413</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7229,10 +7294,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>419</v>
+        <v>307</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7243,45 +7308,45 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>423</v>
+        <v>143</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>424</v>
+        <v>149</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7306,43 +7371,43 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7354,13 +7419,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7371,10 +7436,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7385,7 +7450,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7397,20 +7462,16 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>191</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7434,13 +7495,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>435</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7458,16 +7519,16 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7482,13 +7543,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>345</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7499,10 +7560,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7525,18 +7586,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>440</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7584,7 +7643,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7593,7 +7652,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7611,10 +7670,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7625,10 +7684,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7651,16 +7710,20 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>294</v>
+        <v>192</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -7684,13 +7747,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7708,7 +7771,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7732,13 +7795,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>362</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7772,21 +7835,23 @@
         <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -7810,13 +7875,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -7858,13 +7923,13 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>452</v>
+        <v>362</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7889,7 +7954,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -7898,7 +7963,7 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>454</v>
@@ -7909,10 +7974,10 @@
       <c r="M48" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -7966,7 +8031,7 @@
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -7987,7 +8052,7 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>451</v>
+        <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>458</v>
@@ -8015,7 +8080,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8024,10 +8089,10 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>394</v>
+        <v>303</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>460</v>
@@ -8035,12 +8100,8 @@
       <c r="M49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8094,7 +8155,7 @@
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
@@ -8115,10 +8176,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8129,10 +8190,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8143,7 +8204,7 @@
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8152,18 +8213,20 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>294</v>
+        <v>464</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>295</v>
+        <v>465</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8212,19 +8275,19 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>297</v>
+        <v>463</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -8239,10 +8302,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>298</v>
+        <v>469</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8253,14 +8316,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8276,19 +8339,19 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>471</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>141</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>301</v>
+        <v>473</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>143</v>
+        <v>474</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8338,7 +8401,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>304</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8350,7 +8413,7 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8365,10 +8428,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>298</v>
+        <v>475</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8379,14 +8442,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8399,25 +8462,25 @@
         <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>140</v>
+        <v>411</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>143</v>
+        <v>479</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>149</v>
+        <v>480</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8466,7 +8529,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>408</v>
+        <v>476</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8478,7 +8541,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8493,10 +8556,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>137</v>
+        <v>482</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8507,10 +8570,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8518,7 +8581,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>94</v>
@@ -8530,23 +8593,19 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>191</v>
+        <v>303</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>304</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8570,13 +8629,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>473</v>
+        <v>84</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -8594,10 +8653,10 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>306</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>94</v>
@@ -8606,7 +8665,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8618,16 +8677,16 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>217</v>
+        <v>307</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -8635,21 +8694,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -8658,23 +8717,21 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>310</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8722,19 +8779,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>313</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -8746,62 +8803,62 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>481</v>
+        <v>423</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>482</v>
+        <v>424</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>483</v>
+        <v>143</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>331</v>
+        <v>149</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8826,13 +8883,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>484</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>332</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -8850,19 +8907,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -8877,10 +8934,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -8898,14 +8955,14 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -8914,22 +8971,22 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>337</v>
+        <v>487</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>338</v>
+        <v>488</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>339</v>
+        <v>489</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>340</v>
+        <v>213</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -8954,13 +9011,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>211</v>
+        <v>376</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>341</v>
+        <v>490</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>342</v>
+        <v>216</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -8981,10 +9038,10 @@
         <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>84</v>
@@ -9002,27 +9059,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>343</v>
+        <v>491</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>344</v>
+        <v>220</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>345</v>
+        <v>221</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>84</v>
+        <v>222</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9033,7 +9090,7 @@
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9042,22 +9099,22 @@
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>397</v>
+        <v>495</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>398</v>
+        <v>292</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9106,13 +9163,13 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
@@ -9130,23 +9187,407 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>400</v>
+        <v>296</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>401</v>
+        <v>297</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR58" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR59" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR60" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR57">
+  <autoFilter ref="A1:AR60">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9156,7 +9597,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1026,6 +1026,9 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_MicrobiologyUrineScreenResult](ConceptMap-VF-MicrobiologyUrineScreenResult.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/MicrobiologyUrineScreenResult</t>
@@ -1953,7 +1956,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="96.6875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="54.56640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -5593,9 +5596,11 @@
       <c r="X29" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y29" s="2"/>
+      <c r="Y29" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5613,7 +5618,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5628,10 +5633,10 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>84</v>
@@ -5640,10 +5645,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5654,10 +5659,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5683,16 +5688,16 @@
         <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5741,7 +5746,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5768,10 +5773,10 @@
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5782,13 +5787,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>287</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>84</v>
@@ -5810,7 +5815,7 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>289</v>
@@ -5886,7 +5891,7 @@
         <v>294</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -5912,13 +5917,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>287</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>84</v>
@@ -6016,7 +6021,7 @@
         <v>294</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
@@ -6042,10 +6047,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6071,16 +6076,16 @@
         <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6109,7 +6114,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6127,7 +6132,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6136,13 +6141,13 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6157,7 +6162,7 @@
         <v>137</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6168,14 +6173,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6197,16 +6202,16 @@
         <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6234,10 +6239,10 @@
         <v>214</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -6255,7 +6260,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6279,27 +6284,27 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6322,19 +6327,19 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6383,7 +6388,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6410,10 +6415,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6424,10 +6429,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6453,13 +6458,13 @@
         <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6485,13 +6490,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6509,7 +6514,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6533,27 +6538,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6579,16 +6584,16 @@
         <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6613,13 +6618,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6637,7 +6642,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6664,10 +6669,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6678,10 +6683,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6704,16 +6709,16 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6763,7 +6768,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6787,27 +6792,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6830,16 +6835,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6889,7 +6894,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6913,27 +6918,27 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6956,19 +6961,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7017,7 +7022,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7029,7 +7034,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7044,10 +7049,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7058,10 +7063,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7182,10 +7187,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7308,14 +7313,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7337,10 +7342,10 @@
         <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>143</v>
@@ -7395,7 +7400,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7436,10 +7441,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7462,13 +7467,13 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7519,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7528,7 +7533,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7546,10 +7551,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7560,10 +7565,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7586,13 +7591,13 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7643,7 +7648,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7652,7 +7657,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7670,10 +7675,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7684,10 +7689,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7713,16 +7718,16 @@
         <v>192</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7750,10 +7755,10 @@
         <v>118</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7771,7 +7776,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7795,13 +7800,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7812,10 +7817,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7841,16 +7846,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -7875,13 +7880,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -7899,7 +7904,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7923,13 +7928,13 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7940,10 +7945,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7966,17 +7971,17 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8025,7 +8030,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8055,7 +8060,7 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8066,10 +8071,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8095,10 +8100,10 @@
         <v>303</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8149,7 +8154,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8176,10 +8181,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8190,10 +8195,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8216,16 +8221,16 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8275,7 +8280,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8302,10 +8307,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8316,10 +8321,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8342,16 +8347,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8401,7 +8406,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8428,10 +8433,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8442,10 +8447,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8468,19 +8473,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8529,7 +8534,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8556,10 +8561,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8570,10 +8575,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8694,10 +8699,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8820,14 +8825,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8849,10 +8854,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -8907,7 +8912,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8948,10 +8953,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8977,13 +8982,13 @@
         <v>192</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>213</v>
@@ -9011,10 +9016,10 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>216</v>
@@ -9035,7 +9040,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>94</v>
@@ -9059,7 +9064,7 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>220</v>
@@ -9076,10 +9081,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9105,13 +9110,13 @@
         <v>288</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>292</v>
@@ -9163,7 +9168,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9187,7 +9192,7 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>296</v>
@@ -9204,10 +9209,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9233,16 +9238,16 @@
         <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9270,10 +9275,10 @@
         <v>214</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9291,7 +9296,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9300,7 +9305,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9321,7 +9326,7 @@
         <v>137</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9332,14 +9337,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9361,16 +9366,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9398,10 +9403,10 @@
         <v>214</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9419,7 +9424,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9443,27 +9448,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9489,16 +9494,16 @@
         <v>85</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9547,7 +9552,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9574,10 +9579,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2380" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,9 +642,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>2074: target not supported</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -1074,28 +1071,6 @@
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>2079: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>2080: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1929,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR60"/>
+  <dimension ref="A1:AR58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
@@ -3851,25 +3826,25 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AL15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3877,13 +3852,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>84</v>
@@ -3927,7 +3902,7 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>84</v>
@@ -3981,7 +3956,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -3996,10 +3971,10 @@
         <v>84</v>
       </c>
       <c r="AP16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AQ16" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4007,14 +3982,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4036,16 +4011,16 @@
         <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -4070,14 +4045,14 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
       </c>
@@ -4094,7 +4069,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>94</v>
@@ -4109,36 +4084,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AQ17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4161,19 +4136,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4222,7 +4197,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4237,25 +4212,25 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4263,10 +4238,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4289,16 +4264,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4348,7 +4323,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4375,13 +4350,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4389,14 +4364,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4415,19 +4390,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4476,7 +4451,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4497,19 +4472,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4517,14 +4492,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4543,19 +4518,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4592,7 +4567,7 @@
         <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
@@ -4602,7 +4577,7 @@
         <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4611,31 +4586,31 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AK21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AP21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4643,16 +4618,16 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="D22" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4671,19 +4646,19 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4732,7 +4707,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4741,31 +4716,31 @@
         <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AJ22" t="s" s="2">
+      <c r="AK22" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AK22" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AP22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4773,10 +4748,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4799,16 +4774,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4858,7 +4833,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4885,13 +4860,13 @@
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4899,10 +4874,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4925,17 +4900,17 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4984,7 +4959,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5005,19 +4980,19 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5025,10 +5000,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5051,19 +5026,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5100,7 +5075,7 @@
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5110,7 +5085,7 @@
         <v>200</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5119,45 +5094,45 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AJ25" t="s" s="2">
+      <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AK25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>84</v>
@@ -5182,16 +5157,16 @@
         <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5240,7 +5215,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5249,42 +5224,42 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AK26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AK26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>298</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5307,13 +5282,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5364,7 +5339,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5394,7 +5369,7 @@
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5405,10 +5380,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5437,7 +5412,7 @@
         <v>141</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>143</v>
@@ -5478,10 +5453,10 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AC28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
@@ -5490,7 +5465,7 @@
         <v>200</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5520,7 +5495,7 @@
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5531,10 +5506,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5557,19 +5532,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5597,28 +5572,28 @@
         <v>183</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5633,22 +5608,22 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5659,10 +5634,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5685,19 +5660,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5746,7 +5721,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5773,10 +5748,10 @@
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5787,14 +5762,12 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>84</v>
       </c>
@@ -5812,22 +5785,22 @@
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>291</v>
-      </c>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5852,13 +5825,11 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5876,7 +5847,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5885,13 +5856,13 @@
         <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>293</v>
+        <v>342</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -5900,64 +5871,62 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>303</v>
+        <v>192</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>289</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5982,13 +5951,13 @@
         <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>84</v>
+        <v>351</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>84</v>
@@ -6006,22 +5975,22 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>287</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
@@ -6030,27 +5999,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>295</v>
+        <v>353</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>296</v>
+        <v>354</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>298</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6061,10 +6030,10 @@
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
@@ -6073,19 +6042,19 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>358</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6110,11 +6079,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>349</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6132,22 +6103,22 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6159,10 +6130,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>137</v>
+        <v>363</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6173,21 +6144,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>84</v>
@@ -6202,17 +6173,15 @@
         <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6236,13 +6205,13 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>214</v>
+        <v>369</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -6260,13 +6229,13 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>84</v>
@@ -6284,27 +6253,27 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6315,7 +6284,7 @@
         <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>84</v>
@@ -6327,19 +6296,19 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>366</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6364,13 +6333,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6388,13 +6357,13 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
@@ -6415,10 +6384,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6429,10 +6398,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6455,16 +6424,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>192</v>
+        <v>386</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6490,13 +6459,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6514,7 +6483,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6538,27 +6507,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6581,20 +6550,18 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>395</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6618,13 +6585,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>390</v>
+        <v>84</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6642,7 +6609,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6666,27 +6633,27 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6697,7 +6664,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -6709,18 +6676,20 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6768,19 +6737,19 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>409</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6792,27 +6761,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6835,17 +6804,15 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>403</v>
+        <v>302</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>404</v>
+        <v>303</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6894,7 +6861,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>402</v>
+        <v>305</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6906,7 +6873,7 @@
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -6918,31 +6885,31 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6961,20 +6928,18 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>412</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>413</v>
+        <v>141</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>414</v>
+        <v>309</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7022,7 +6987,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>411</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7034,7 +6999,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>417</v>
+        <v>145</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7049,10 +7014,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>419</v>
+        <v>306</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7063,42 +7028,46 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7146,19 +7115,19 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>306</v>
+        <v>418</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>84</v>
@@ -7176,7 +7145,7 @@
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7187,21 +7156,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>84</v>
@@ -7213,17 +7182,15 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>140</v>
+        <v>420</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>141</v>
+        <v>421</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7272,19 +7239,19 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7299,10 +7266,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>307</v>
+        <v>425</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7313,46 +7280,42 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>140</v>
+        <v>420</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7406,13 +7369,13 @@
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7427,10 +7390,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>137</v>
+        <v>429</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7441,10 +7404,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7467,16 +7430,20 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7500,13 +7467,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7524,7 +7491,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7533,7 +7500,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7548,13 +7515,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>433</v>
+        <v>355</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7565,10 +7532,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7579,7 +7546,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7591,16 +7558,20 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>428</v>
+        <v>192</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7624,13 +7595,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7648,16 +7619,16 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7672,13 +7643,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>355</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7689,10 +7660,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7715,19 +7686,17 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>192</v>
+        <v>447</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7752,13 +7721,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7776,7 +7745,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7800,13 +7769,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>446</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>363</v>
+        <v>451</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7817,10 +7786,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7831,7 +7800,7 @@
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -7843,20 +7812,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>302</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -7880,37 +7845,37 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
@@ -7928,13 +7893,13 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>363</v>
+        <v>455</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7945,10 +7910,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7959,7 +7924,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -7968,21 +7933,21 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8030,13 +7995,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8057,10 +8022,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8071,10 +8036,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8085,7 +8050,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8094,18 +8059,20 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>303</v>
+        <v>464</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8154,13 +8121,13 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
@@ -8181,10 +8148,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8195,10 +8162,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8221,18 +8188,20 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>465</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8280,7 +8249,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8307,10 +8276,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8321,10 +8290,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8335,7 +8304,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8344,20 +8313,18 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>472</v>
+        <v>302</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>473</v>
+        <v>303</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8406,19 +8373,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>305</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8433,10 +8400,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>476</v>
+        <v>306</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8454,7 +8421,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8470,23 +8437,21 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>412</v>
+        <v>140</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>478</v>
+        <v>141</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>479</v>
+        <v>309</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8534,7 +8499,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>477</v>
+        <v>312</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8546,7 +8511,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8561,10 +8526,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>483</v>
+        <v>306</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8575,42 +8540,46 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8658,19 +8627,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>306</v>
+        <v>418</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8688,7 +8657,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>307</v>
+        <v>137</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8699,21 +8668,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -8722,21 +8691,23 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>480</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>310</v>
+        <v>481</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8760,13 +8731,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -8784,19 +8755,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>313</v>
+        <v>479</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -8808,16 +8779,16 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>307</v>
+        <v>220</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>84</v>
+        <v>221</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -8825,45 +8796,45 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>424</v>
+        <v>486</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>143</v>
+        <v>488</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>149</v>
+        <v>291</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -8912,19 +8883,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>426</v>
+        <v>485</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -8936,27 +8907,27 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8964,7 +8935,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>94</v>
@@ -8976,22 +8947,22 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>213</v>
+        <v>340</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9016,13 +8987,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>377</v>
+        <v>213</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>216</v>
+        <v>341</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9040,16 +9011,16 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9064,16 +9035,16 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>492</v>
+        <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>221</v>
+        <v>344</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -9081,21 +9052,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9104,22 +9075,22 @@
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>494</v>
+        <v>347</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>495</v>
+        <v>348</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>496</v>
+        <v>349</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9144,13 +9115,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>84</v>
+        <v>351</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9168,13 +9139,13 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
@@ -9192,27 +9163,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>497</v>
+        <v>353</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>296</v>
+        <v>354</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>298</v>
+        <v>356</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9223,7 +9194,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9235,19 +9206,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="N58" t="s" s="2">
-        <v>501</v>
+        <v>407</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>348</v>
+        <v>408</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9272,13 +9243,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>502</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>349</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9296,16 +9267,16 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>503</v>
+        <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9323,276 +9294,20 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>137</v>
+        <v>410</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR60" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR60">
+  <autoFilter ref="A1:AR58">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9602,7 +9317,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservationurine.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
